--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260728.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260728.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>144,482</t>
+          <t>157,499</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>157,499</t>
+          <t>144,482</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,218,076</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,218,076</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,603,400</t>
+          <t>96,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>1,603,400</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>234,000</t>
+          <t>511,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>511,000</t>
+          <t>234,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>401,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,031,121</t>
+          <t>67,538</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,807,000</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>67,538</t>
+          <t>1,031,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>401,000</t>
+          <t>1,807,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>340,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>340,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>161,000</t>
+          <t>183,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>699,000</t>
+          <t>261,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>183,000</t>
+          <t>161,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>261,000</t>
+          <t>699,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
